--- a/artfynd/A 18378-2026 artfynd.xlsx
+++ b/artfynd/A 18378-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY54"/>
+  <dimension ref="A1:AY66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>86778658</v>
+        <v>87556027</v>
       </c>
       <c r="B2" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56895</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219798</v>
+        <v>100088</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Vanlig snok</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Natrix natrix</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -715,24 +710,29 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Nynäshamn, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>669370.9202235858</v>
+        <v>669345</v>
       </c>
       <c r="R2" t="n">
-        <v>6536913.694616597</v>
+        <v>6536922</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -756,22 +756,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-07-10</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-08-20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-07-10</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-08-20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,27 +776,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Thomas Strid</t>
+          <t>Martin Olofsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Thomas Strid</t>
+          <t>Martin Olofsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>86778677</v>
+        <v>87664529</v>
       </c>
       <c r="B3" t="n">
-        <v>103178</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>9414</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -814,45 +799,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221141</v>
+        <v>105076</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Noshornsoxe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Sinodendron cylindricum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Nynäshamn, Srm</t>
+          <t>Kalvö 1:6, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>669376.8824140296</v>
+        <v>669238</v>
       </c>
       <c r="R3" t="n">
-        <v>6536895.869827067</v>
+        <v>6536882</v>
       </c>
       <c r="S3" t="n">
         <v>12</v>
@@ -879,22 +853,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2020-07-10</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-06-23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2020-07-10</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-07-15</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Kalvö 1:6, beställare: Nynäshamns kommun</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,27 +878,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Thomas Strid</t>
+          <t>Lilian Karlsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Thomas Strid</t>
+          <t>Lilian Karlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>86777385</v>
+        <v>131580328</v>
       </c>
       <c r="B4" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56854</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -937,52 +901,58 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219798</v>
+        <v>205995</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>knoppbristning</t>
-        </is>
-      </c>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Nynäshamn, Srm</t>
+          <t>Stora Grönvik, Nynäshamn, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>669070.891712066</v>
+        <v>669316</v>
       </c>
       <c r="R4" t="n">
-        <v>6536849.33033889</v>
+        <v>6536931</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1006,22 +976,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2020-07-10</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2020-07-10</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1036,27 +1006,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Thomas Strid</t>
+          <t>Martin Berg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Thomas Strid</t>
+          <t>Martin Berg, Saga Samuelsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>86778399</v>
+        <v>87664488</v>
       </c>
       <c r="B5" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56905</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1064,52 +1029,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219798</v>
+        <v>208260</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Huggorm</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Vipera berus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>knoppbristning</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Nynäshamn, Srm</t>
+          <t>Kalvö 1:6, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>669312.7880782534</v>
+        <v>669391</v>
       </c>
       <c r="R5" t="n">
-        <v>6536940.591071493</v>
+        <v>6536920</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1133,22 +1088,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2020-07-10</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-07-15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2020-07-10</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-07-15</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Kalvö 1:6, beställare: Nynäshamns kommun</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1163,27 +1113,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Thomas Strid</t>
+          <t>Lilian Karlsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Thomas Strid</t>
+          <t>Lilian Karlsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>87555754</v>
+        <v>87664512</v>
       </c>
       <c r="B6" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56905</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1191,52 +1136,46 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219798</v>
+        <v>208260</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Huggorm</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Vipera berus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>årsunge</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nynäshamn, Srm</t>
+          <t>Kalvö 1:6, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>669321.9125210897</v>
+        <v>669287</v>
       </c>
       <c r="R6" t="n">
-        <v>6536886.214065194</v>
+        <v>6536802</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1260,22 +1199,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2020-08-20</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>15:11</t>
+          <t>2020-06-23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2020-08-20</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>15:11</t>
+          <t>2020-07-15</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Kalvö 1:6, beställare: Nynäshamns kommun</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1284,33 +1218,29 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Hanna Lilja</t>
+          <t>Lilian Karlsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Hanna Lilja</t>
+          <t>Lilian Karlsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>87556462</v>
+        <v>86777385</v>
       </c>
       <c r="B7" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1337,7 +1267,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1347,7 +1277,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>knoppbristning</t>
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
@@ -1357,10 +1287,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>669068.9981188406</v>
+        <v>669071</v>
       </c>
       <c r="R7" t="n">
-        <v>6536809.971164657</v>
+        <v>6536849</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1387,22 +1317,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2020-08-20</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>16:18</t>
+          <t>2020-07-10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2020-08-20</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>16:18</t>
+          <t>2020-07-10</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1417,27 +1337,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Hanna Lilja</t>
+          <t>Thomas Strid</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Hanna Lilja</t>
+          <t>Thomas Strid</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>87555664</v>
+        <v>86778399</v>
       </c>
       <c r="B8" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1464,7 +1379,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1474,7 +1389,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>knoppbristning</t>
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
@@ -1484,13 +1399,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>669307.1430844115</v>
+        <v>669313</v>
       </c>
       <c r="R8" t="n">
-        <v>6536810.112535363</v>
+        <v>6536941</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1514,22 +1429,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2020-08-20</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-07-10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2020-08-20</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-07-10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1544,27 +1449,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Martin Olofsson</t>
+          <t>Thomas Strid</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Martin Olofsson</t>
+          <t>Thomas Strid</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>87556748</v>
+        <v>86778658</v>
       </c>
       <c r="B9" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1591,7 +1491,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1599,11 +1499,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1611,13 +1507,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>669084.8981413587</v>
+        <v>669371</v>
       </c>
       <c r="R9" t="n">
-        <v>6536825.140355954</v>
+        <v>6536914</v>
       </c>
       <c r="S9" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1641,22 +1537,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2020-08-20</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>16:32</t>
+          <t>2020-07-10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2020-08-20</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>16:32</t>
+          <t>2020-07-10</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1671,27 +1557,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Hanna Lilja</t>
+          <t>Thomas Strid</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Hanna Lilja</t>
+          <t>Thomas Strid</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>87556027</v>
+        <v>87554993</v>
       </c>
       <c r="B10" t="n">
-        <v>57140</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1699,53 +1580,47 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100088</v>
+        <v>219798</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vanlig snok</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Natrix natrix</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>ex.</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>årsunge</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Nynäshamn, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>669345.1927652942</v>
+        <v>669286</v>
       </c>
       <c r="R10" t="n">
-        <v>6536921.863606206</v>
+        <v>6536769</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1774,7 +1649,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1784,7 +1659,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1799,27 +1674,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Martin Olofsson</t>
+          <t>Hanna Lilja</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Martin Olofsson</t>
+          <t>Hanna Lilja</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>87556485</v>
+        <v>87555100</v>
       </c>
       <c r="B11" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1846,7 +1716,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1854,7 +1724,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1862,13 +1736,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>669057.5945422223</v>
+        <v>669295</v>
       </c>
       <c r="R11" t="n">
-        <v>6536786.730962827</v>
+        <v>6536764</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1897,7 +1771,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1907,7 +1781,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1922,27 +1796,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Martin Olofsson</t>
+          <t>Hanna Lilja</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Martin Olofsson</t>
+          <t>Hanna Lilja</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>87556145</v>
+        <v>87555212</v>
       </c>
       <c r="B12" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1969,12 +1838,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1989,13 +1853,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>669105.1918794678</v>
+        <v>669319</v>
       </c>
       <c r="R12" t="n">
-        <v>6536916.986569878</v>
+        <v>6536769</v>
       </c>
       <c r="S12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2024,7 +1888,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2034,7 +1898,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2061,15 +1925,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>87556173</v>
+        <v>87555228</v>
       </c>
       <c r="B13" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2096,7 +1955,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2116,13 +1975,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>669087.1948729876</v>
+        <v>669329</v>
       </c>
       <c r="R13" t="n">
-        <v>6536867.101046971</v>
+        <v>6536781</v>
       </c>
       <c r="S13" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2151,7 +2010,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2161,7 +2020,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2188,15 +2047,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>87555519</v>
+        <v>87555248</v>
       </c>
       <c r="B14" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2238,13 +2092,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>669260.0134674031</v>
+        <v>669316</v>
       </c>
       <c r="R14" t="n">
-        <v>6536798.735588402</v>
+        <v>6536786</v>
       </c>
       <c r="S14" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2273,7 +2127,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2283,7 +2137,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2310,15 +2164,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>87556777</v>
+        <v>87555369</v>
       </c>
       <c r="B15" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2345,7 +2194,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2365,10 +2214,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>669107.6967950047</v>
+        <v>669296</v>
       </c>
       <c r="R15" t="n">
-        <v>6536836.478623262</v>
+        <v>6536810</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2398,19 +2247,9 @@
           <t>2020-08-20</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2020-08-20</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2437,15 +2276,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>87557077</v>
+        <v>87555461</v>
       </c>
       <c r="B16" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2472,7 +2306,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -2487,13 +2321,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>669215.9627707668</v>
+        <v>669292</v>
       </c>
       <c r="R16" t="n">
-        <v>6536835.039639707</v>
+        <v>6536774</v>
       </c>
       <c r="S16" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2522,7 +2356,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2532,7 +2366,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2559,15 +2393,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>87556190</v>
+        <v>87555491</v>
       </c>
       <c r="B17" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2594,7 +2423,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2614,10 +2443,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>669096.1830976584</v>
+        <v>669307</v>
       </c>
       <c r="R17" t="n">
-        <v>6536862.845211352</v>
+        <v>6536810</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2647,19 +2476,9 @@
           <t>2020-08-20</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2020-08-20</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2686,15 +2505,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>87556049</v>
+        <v>87555519</v>
       </c>
       <c r="B18" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2724,11 +2538,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K18" t="inlineStr">
         <is>
           <t>överblommad</t>
@@ -2741,13 +2550,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>669233.859195988</v>
+        <v>669260</v>
       </c>
       <c r="R18" t="n">
-        <v>6537004.813795959</v>
+        <v>6536799</v>
       </c>
       <c r="S18" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2776,7 +2585,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2786,7 +2595,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2813,15 +2622,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>87556392</v>
+        <v>87555538</v>
       </c>
       <c r="B19" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2848,12 +2652,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2868,13 +2667,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>669070.5482775499</v>
+        <v>669244</v>
       </c>
       <c r="R19" t="n">
-        <v>6536810.039316466</v>
+        <v>6536810</v>
       </c>
       <c r="S19" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2903,7 +2702,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2913,7 +2712,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2943,12 +2742,7 @@
         <v>87555569</v>
       </c>
       <c r="B20" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2995,10 +2789,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>669256.2039691125</v>
+        <v>669256</v>
       </c>
       <c r="R20" t="n">
-        <v>6536826.47476024</v>
+        <v>6536826</v>
       </c>
       <c r="S20" t="n">
         <v>14</v>
@@ -3067,15 +2861,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>87555911</v>
+        <v>87555609</v>
       </c>
       <c r="B21" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3117,13 +2906,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>669353.8117404103</v>
+        <v>669260</v>
       </c>
       <c r="R21" t="n">
-        <v>6536984.773061069</v>
+        <v>6536816</v>
       </c>
       <c r="S21" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3152,7 +2941,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3162,7 +2951,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3189,15 +2978,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>87557344</v>
+        <v>87555630</v>
       </c>
       <c r="B22" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3224,7 +3008,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3244,13 +3028,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>669235.1398994651</v>
+        <v>669281</v>
       </c>
       <c r="R22" t="n">
-        <v>6536905.132767012</v>
+        <v>6536850</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3279,7 +3063,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3289,7 +3073,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3316,15 +3100,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>87557201</v>
+        <v>87555754</v>
       </c>
       <c r="B23" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3351,7 +3130,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3371,13 +3150,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>669204.8061589758</v>
+        <v>669322</v>
       </c>
       <c r="R23" t="n">
-        <v>6536865.03920526</v>
+        <v>6536886</v>
       </c>
       <c r="S23" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3406,7 +3185,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3416,7 +3195,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3443,15 +3222,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>87555369</v>
+        <v>87555882</v>
       </c>
       <c r="B24" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3478,7 +3252,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3498,10 +3272,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>669295.7752425292</v>
+        <v>669345</v>
       </c>
       <c r="R24" t="n">
-        <v>6536809.612070384</v>
+        <v>6536922</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3531,19 +3305,9 @@
           <t>2020-08-20</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2020-08-20</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3570,15 +3334,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>87556102</v>
+        <v>87555911</v>
       </c>
       <c r="B25" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3605,15 +3364,14 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3621,13 +3379,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>669138.1248966013</v>
+        <v>669354</v>
       </c>
       <c r="R25" t="n">
-        <v>6536921.53561414</v>
+        <v>6536985</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3656,7 +3414,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3666,7 +3424,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3681,12 +3439,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Martin Olofsson</t>
+          <t>Hanna Lilja</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Martin Olofsson</t>
+          <t>Hanna Lilja</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3696,12 +3454,7 @@
         <v>87555929</v>
       </c>
       <c r="B26" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3748,10 +3501,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>669353.0848592694</v>
+        <v>669353</v>
       </c>
       <c r="R26" t="n">
-        <v>6537001.277708953</v>
+        <v>6537001</v>
       </c>
       <c r="S26" t="n">
         <v>12</v>
@@ -3820,15 +3573,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>87555882</v>
+        <v>87556049</v>
       </c>
       <c r="B27" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3855,7 +3603,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3875,13 +3623,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>669345.1927652942</v>
+        <v>669234</v>
       </c>
       <c r="R27" t="n">
-        <v>6536921.863606206</v>
+        <v>6537005</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3910,7 +3658,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3920,7 +3668,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3935,27 +3683,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Martin Olofsson</t>
+          <t>Hanna Lilja</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Martin Olofsson</t>
+          <t>Hanna Lilja</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>87555630</v>
+        <v>87556102</v>
       </c>
       <c r="B28" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3982,7 +3725,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3990,11 +3733,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -4002,13 +3741,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>669281.0635370397</v>
+        <v>669138</v>
       </c>
       <c r="R28" t="n">
-        <v>6536849.790966302</v>
+        <v>6536922</v>
       </c>
       <c r="S28" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4035,19 +3774,9 @@
           <t>2020-08-20</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>15:01</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2020-08-20</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>15:01</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4062,27 +3791,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Hanna Lilja</t>
+          <t>Martin Olofsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Hanna Lilja</t>
+          <t>Martin Olofsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>87557271</v>
+        <v>87556145</v>
       </c>
       <c r="B29" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4109,7 +3833,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -4129,13 +3853,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>669191.2756342588</v>
+        <v>669105</v>
       </c>
       <c r="R29" t="n">
-        <v>6536878.397064824</v>
+        <v>6536917</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4164,7 +3888,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4174,7 +3898,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4189,27 +3913,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Martin Olofsson</t>
+          <t>Hanna Lilja</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Martin Olofsson</t>
+          <t>Hanna Lilja</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>87556824</v>
+        <v>87556173</v>
       </c>
       <c r="B30" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4236,7 +3955,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4256,13 +3975,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>669143.4710889653</v>
+        <v>669087</v>
       </c>
       <c r="R30" t="n">
-        <v>6536870.609483276</v>
+        <v>6536867</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4291,7 +4010,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4301,7 +4020,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4328,15 +4047,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>87556251</v>
+        <v>87556190</v>
       </c>
       <c r="B31" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4363,7 +4077,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4383,13 +4097,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>669098.5901557235</v>
+        <v>669096</v>
       </c>
       <c r="R31" t="n">
-        <v>6536855.199281443</v>
+        <v>6536863</v>
       </c>
       <c r="S31" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4416,19 +4130,9 @@
           <t>2020-08-20</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>16:12</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2020-08-20</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>16:12</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4443,27 +4147,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Hanna Lilja</t>
+          <t>Martin Olofsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Hanna Lilja</t>
+          <t>Martin Olofsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>87557237</v>
+        <v>87556251</v>
       </c>
       <c r="B32" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4490,7 +4189,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4510,13 +4209,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>669208.2869743831</v>
+        <v>669099</v>
       </c>
       <c r="R32" t="n">
-        <v>6536868.293076636</v>
+        <v>6536855</v>
       </c>
       <c r="S32" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4545,7 +4244,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4555,7 +4254,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4582,15 +4281,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>87557291</v>
+        <v>87556392</v>
       </c>
       <c r="B33" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4617,7 +4311,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4637,13 +4331,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>669199.7646902569</v>
+        <v>669071</v>
       </c>
       <c r="R33" t="n">
-        <v>6536885.488750233</v>
+        <v>6536810</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4672,7 +4366,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4682,7 +4376,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4709,15 +4403,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>87555538</v>
+        <v>87556462</v>
       </c>
       <c r="B34" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4744,7 +4433,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -4759,13 +4453,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>669243.9897222875</v>
+        <v>669069</v>
       </c>
       <c r="R34" t="n">
-        <v>6536809.916626822</v>
+        <v>6536810</v>
       </c>
       <c r="S34" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4794,7 +4488,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4804,7 +4498,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4831,15 +4525,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>87556734</v>
+        <v>87556485</v>
       </c>
       <c r="B35" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4866,7 +4555,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4874,11 +4563,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4886,13 +4571,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>669080.5829760955</v>
+        <v>669058</v>
       </c>
       <c r="R35" t="n">
-        <v>6536829.084938368</v>
+        <v>6536787</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4919,19 +4604,9 @@
           <t>2020-08-20</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>16:29</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2020-08-20</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>16:29</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4946,12 +4621,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Hanna Lilja</t>
+          <t>Martin Olofsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Hanna Lilja</t>
+          <t>Martin Olofsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4961,12 +4636,7 @@
         <v>87556505</v>
       </c>
       <c r="B36" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5013,10 +4683,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>669062.285581822</v>
+        <v>669062</v>
       </c>
       <c r="R36" t="n">
-        <v>6536797.789847642</v>
+        <v>6536798</v>
       </c>
       <c r="S36" t="n">
         <v>12</v>
@@ -5085,15 +4755,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>87555609</v>
+        <v>87556734</v>
       </c>
       <c r="B37" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5120,7 +4785,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -5135,13 +4805,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>669259.7810189973</v>
+        <v>669081</v>
       </c>
       <c r="R37" t="n">
-        <v>6536815.779562297</v>
+        <v>6536829</v>
       </c>
       <c r="S37" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5170,7 +4840,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5180,7 +4850,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5207,15 +4877,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>87664522</v>
+        <v>87556748</v>
       </c>
       <c r="B38" t="n">
-        <v>96313</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5223,22 +4888,26 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>223609</v>
+        <v>219798</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vanlig skogsknipprot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Epipactis helleborine subsp. helleborine</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr"/>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -5246,19 +4915,25 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Kalvö 1:6, Srm</t>
+          <t>Nynäshamn, Srm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>669218.8587999297</v>
+        <v>669085</v>
       </c>
       <c r="R38" t="n">
-        <v>6536839.818179557</v>
+        <v>6536825</v>
       </c>
       <c r="S38" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5282,27 +4957,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2020-06-23</t>
+          <t>2020-08-20</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2020-07-15</t>
+          <t>2020-08-20</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Kalvö 1:6, beställare: Nynäshamns kommun</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5317,27 +4987,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Lilian Karlsson</t>
+          <t>Hanna Lilja</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Lilian Karlsson</t>
+          <t>Hanna Lilja</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>87664492</v>
+        <v>87556777</v>
       </c>
       <c r="B39" t="n">
-        <v>103178</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5345,37 +5010,52 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221141</v>
+        <v>219798</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Kalvö 1:6, Srm</t>
+          <t>Nynäshamn, Srm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>669367.8427026655</v>
+        <v>669108</v>
       </c>
       <c r="R39" t="n">
-        <v>6536913.042289116</v>
+        <v>6536836</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5399,27 +5079,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2020-07-15</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-08-20</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2020-07-15</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Kalvö 1:6, beställare: Nynäshamns kommun</t>
+          <t>2020-08-20</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5434,27 +5099,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Lilian Karlsson</t>
+          <t>Martin Olofsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Lilian Karlsson</t>
+          <t>Martin Olofsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>87664500</v>
+        <v>87556824</v>
       </c>
       <c r="B40" t="n">
-        <v>103178</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5462,37 +5122,52 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221141</v>
+        <v>219798</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Kalvö 1:6, Srm</t>
+          <t>Nynäshamn, Srm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>669365.9291184511</v>
+        <v>669143</v>
       </c>
       <c r="R40" t="n">
-        <v>6536921.226503544</v>
+        <v>6536871</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5516,27 +5191,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2020-06-23</t>
+          <t>2020-08-20</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2020-06-23</t>
+          <t>2020-08-20</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Kalvö 1:6, beställare: Nynäshamns kommun</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5551,27 +5221,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Lilian Karlsson</t>
+          <t>Hanna Lilja</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Lilian Karlsson</t>
+          <t>Hanna Lilja</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>87664512</v>
+        <v>87557077</v>
       </c>
       <c r="B41" t="n">
-        <v>57150</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5579,46 +5244,47 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>208260</v>
+        <v>219798</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Huggorm</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Vipera berus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>årsunge</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Kalvö 1:6, Srm</t>
+          <t>Nynäshamn, Srm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>669286.7921596202</v>
+        <v>669216</v>
       </c>
       <c r="R41" t="n">
-        <v>6536801.981491813</v>
+        <v>6536835</v>
       </c>
       <c r="S41" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5642,27 +5308,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2020-06-23</t>
+          <t>2020-08-20</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2020-07-15</t>
+          <t>2020-08-20</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Kalvö 1:6, beställare: Nynäshamns kommun</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5671,34 +5332,28 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Lilian Karlsson</t>
+          <t>Hanna Lilja</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Lilian Karlsson</t>
+          <t>Hanna Lilja</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>87664491</v>
+        <v>87557201</v>
       </c>
       <c r="B42" t="n">
-        <v>96313</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5706,33 +5361,52 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>223609</v>
+        <v>219798</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vanlig skogsknipprot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Epipactis helleborine subsp. helleborine</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Kalvö 1:6, Srm</t>
+          <t>Nynäshamn, Srm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>669364.0440276891</v>
+        <v>669205</v>
       </c>
       <c r="R42" t="n">
-        <v>6536917.009233613</v>
+        <v>6536865</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5756,27 +5430,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2020-07-15</t>
+          <t>2020-08-20</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2020-07-15</t>
+          <t>2020-08-20</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Kalvö 1:6, beställare: Nynäshamns kommun</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5791,27 +5460,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Lilian Karlsson</t>
+          <t>Hanna Lilja</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Lilian Karlsson</t>
+          <t>Hanna Lilja</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>87664486</v>
+        <v>87557237</v>
       </c>
       <c r="B43" t="n">
-        <v>96313</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5819,33 +5483,52 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>223609</v>
+        <v>219798</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vanlig skogsknipprot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Epipactis helleborine subsp. helleborine</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Kalvö 1:6, Srm</t>
+          <t>Nynäshamn, Srm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>669355.0050488989</v>
+        <v>669208</v>
       </c>
       <c r="R43" t="n">
-        <v>6536793.098556938</v>
+        <v>6536868</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5869,27 +5552,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2020-07-15</t>
+          <t>2020-08-20</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2020-07-15</t>
+          <t>2020-08-20</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Kalvö 1:6, beställare: Nynäshamns kommun</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5904,27 +5582,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Lilian Karlsson</t>
+          <t>Hanna Lilja</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Lilian Karlsson</t>
+          <t>Hanna Lilja</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>87664485</v>
+        <v>87557271</v>
       </c>
       <c r="B44" t="n">
-        <v>103178</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5932,37 +5605,52 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221141</v>
+        <v>219798</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Kalvö 1:6, Srm</t>
+          <t>Nynäshamn, Srm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>669366.1003464828</v>
+        <v>669191</v>
       </c>
       <c r="R44" t="n">
-        <v>6536799.788754491</v>
+        <v>6536878</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5986,27 +5674,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2020-07-15</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-08-20</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2020-07-15</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Kalvö 1:6, beställare: Nynäshamns kommun</t>
+          <t>2020-08-20</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6021,27 +5694,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Lilian Karlsson</t>
+          <t>Martin Olofsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Lilian Karlsson</t>
+          <t>Martin Olofsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>87664493</v>
+        <v>87557291</v>
       </c>
       <c r="B45" t="n">
-        <v>96313</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6049,33 +5717,52 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>223609</v>
+        <v>219798</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vanlig skogsknipprot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Epipactis helleborine subsp. helleborine</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Kalvö 1:6, Srm</t>
+          <t>Nynäshamn, Srm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>669266.2566659814</v>
+        <v>669200</v>
       </c>
       <c r="R45" t="n">
-        <v>6536950.945214291</v>
+        <v>6536885</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6099,27 +5786,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2020-06-23</t>
+          <t>2020-08-20</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2020-06-23</t>
+          <t>2020-08-20</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Kalvö 1:6, beställare: Nynäshamns kommun</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6134,27 +5816,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Lilian Karlsson</t>
+          <t>Hanna Lilja</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Lilian Karlsson</t>
+          <t>Hanna Lilja</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>87664527</v>
+        <v>87557344</v>
       </c>
       <c r="B46" t="n">
-        <v>96313</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6162,33 +5839,52 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>223609</v>
+        <v>219798</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vanlig skogsknipprot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Epipactis helleborine subsp. helleborine</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Kalvö 1:6, Srm</t>
+          <t>Nynäshamn, Srm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>669247.0025217986</v>
+        <v>669235</v>
       </c>
       <c r="R46" t="n">
-        <v>6536953.198387931</v>
+        <v>6536905</v>
       </c>
       <c r="S46" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6212,27 +5908,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2020-06-23</t>
+          <t>2020-08-20</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2020-07-15</t>
+          <t>2020-08-20</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Kalvö 1:6, beställare: Nynäshamns kommun</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6247,27 +5938,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Lilian Karlsson</t>
+          <t>Hanna Lilja</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Lilian Karlsson</t>
+          <t>Hanna Lilja</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>87664490</v>
+        <v>87557940</v>
       </c>
       <c r="B47" t="n">
-        <v>96313</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6275,22 +5961,26 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>223609</v>
+        <v>219798</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vanlig skogsknipprot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Epipactis helleborine subsp. helleborine</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr"/>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -6298,19 +5988,25 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Kalvö 1:6, Srm</t>
+          <t>Nynäshamn, Srm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>669353.1250605525</v>
+        <v>669383</v>
       </c>
       <c r="R47" t="n">
-        <v>6536918.078692008</v>
+        <v>6536903</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6334,27 +6030,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2020-07-15</t>
+          <t>2020-08-20</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2020-07-15</t>
+          <t>2020-08-20</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Kalvö 1:6, beställare: Nynäshamns kommun</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6369,27 +6060,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Lilian Karlsson</t>
+          <t>Martin Olofsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Lilian Karlsson</t>
+          <t>Martin Olofsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>87664521</v>
+        <v>86778677</v>
       </c>
       <c r="B48" t="n">
-        <v>96313</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106156</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6397,22 +6083,26 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>223609</v>
+        <v>221141</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vanlig skogsknipprot</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Epipactis helleborine subsp. helleborine</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr"/>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -6420,19 +6110,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Kalvö 1:6, Srm</t>
+          <t>Nynäshamn, Srm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>669286.7921596202</v>
+        <v>669377</v>
       </c>
       <c r="R48" t="n">
-        <v>6536801.981491813</v>
+        <v>6536896</v>
       </c>
       <c r="S48" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6456,27 +6148,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2020-06-23</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-07-10</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2020-07-15</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Kalvö 1:6, beställare: Nynäshamns kommun</t>
+          <t>2020-07-10</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6491,27 +6168,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Lilian Karlsson</t>
+          <t>Thomas Strid</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Lilian Karlsson</t>
+          <t>Thomas Strid</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>87664489</v>
+        <v>87664485</v>
       </c>
       <c r="B49" t="n">
-        <v>96313</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106156</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6519,19 +6191,23 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>223609</v>
+        <v>221141</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vanlig skogsknipprot</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Epipactis helleborine subsp. helleborine</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr"/>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6539,10 +6215,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>669349.1334223857</v>
+        <v>669366</v>
       </c>
       <c r="R49" t="n">
-        <v>6536902.916237375</v>
+        <v>6536800</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -6572,19 +6248,9 @@
           <t>2020-07-15</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2020-07-15</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
@@ -6616,15 +6282,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>87664523</v>
+        <v>87664492</v>
       </c>
       <c r="B50" t="n">
-        <v>96313</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106156</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6632,42 +6293,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>223609</v>
+        <v>221141</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vanlig skogsknipprot</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Epipactis helleborine subsp. helleborine</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Kalvö 1:6, Srm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>669222.8056282718</v>
+        <v>669368</v>
       </c>
       <c r="R50" t="n">
-        <v>6536856.012288704</v>
+        <v>6536913</v>
       </c>
       <c r="S50" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6691,22 +6347,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2020-06-23</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-07-15</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2020-07-15</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
@@ -6738,15 +6384,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>87664526</v>
+        <v>87664500</v>
       </c>
       <c r="B51" t="n">
-        <v>96313</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106156</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6754,19 +6395,23 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>223609</v>
+        <v>221141</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vanlig skogsknipprot</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Epipactis helleborine subsp. helleborine</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr"/>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6774,13 +6419,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>669283.1303957256</v>
+        <v>669366</v>
       </c>
       <c r="R51" t="n">
-        <v>6536849.881949868</v>
+        <v>6536921</v>
       </c>
       <c r="S51" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6807,19 +6452,9 @@
           <t>2020-06-23</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2020-07-15</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-06-23</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
@@ -6851,38 +6486,37 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>87664496</v>
+        <v>86778724</v>
       </c>
       <c r="B52" t="n">
-        <v>96313</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102560</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>223609</v>
+        <v>222133</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vanlig skogsknipprot</t>
+          <t>Jungfrulin</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Epipactis helleborine subsp. helleborine</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr"/>
+          <t>Polygala vulgaris</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -6890,19 +6524,25 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Kalvö 1:6, Srm</t>
+          <t>Nynäshamn, Srm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>669258.8412329623</v>
+        <v>669376</v>
       </c>
       <c r="R52" t="n">
-        <v>6536954.753008895</v>
+        <v>6536875</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6926,27 +6566,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2020-06-23</t>
-        </is>
-      </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-07-10</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2020-06-23</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Kalvö 1:6, beställare: Nynäshamns kommun</t>
+          <t>2020-07-10</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6961,49 +6586,44 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Lilian Karlsson</t>
+          <t>Thomas Strid</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Lilian Karlsson</t>
+          <t>Thomas Strid</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>87664529</v>
+        <v>87664502</v>
       </c>
       <c r="B53" t="n">
-        <v>9310</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102560</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>105076</v>
+        <v>222133</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Noshornsoxe</t>
+          <t>Jungfrulin</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Sinodendron cylindricum</t>
+          <t>Polygala vulgaris</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -7013,13 +6633,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>669238.2281962588</v>
+        <v>669364</v>
       </c>
       <c r="R53" t="n">
-        <v>6536882.013478333</v>
+        <v>6536921</v>
       </c>
       <c r="S53" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7046,19 +6666,9 @@
           <t>2020-06-23</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2020-07-15</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-06-23</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
@@ -7090,69 +6700,48 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131580328</v>
+        <v>87664505</v>
       </c>
       <c r="B54" t="n">
-        <v>56796</v>
+        <v>102560</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>205995</v>
+        <v>222133</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Jungfrulin</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Polygala vulgaris</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>autobox med tidsexpansion</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Stora Grönvik, Nynäshamn, Srm</t>
+          <t>Kalvö 1:6, Srm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>669316</v>
+        <v>669374</v>
       </c>
       <c r="R54" t="n">
-        <v>6536931</v>
+        <v>6536876</v>
       </c>
       <c r="S54" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7176,22 +6765,17 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>21:00</t>
+          <t>2020-06-23</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>04:00</t>
+          <t>2020-06-23</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Kalvö 1:6, beställare: Nynäshamns kommun</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7206,15 +6790,1236 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Martin Berg</t>
+          <t>Lilian Karlsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Martin Berg, Saga Samuelsson</t>
+          <t>Lilian Karlsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>87664486</v>
+      </c>
+      <c r="B55" t="n">
+        <v>99097</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>223609</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Vanlig skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine subsp. helleborine</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Kalvö 1:6, Srm</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>669355</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6536793</v>
+      </c>
+      <c r="S55" t="n">
+        <v>15</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Nynäshamn</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Nynäshamn</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2020-07-15</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2020-07-15</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Kalvö 1:6, beställare: Nynäshamns kommun</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Lilian Karlsson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Lilian Karlsson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>87664489</v>
+      </c>
+      <c r="B56" t="n">
+        <v>99097</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>223609</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Vanlig skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine subsp. helleborine</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Kalvö 1:6, Srm</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>669349</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6536903</v>
+      </c>
+      <c r="S56" t="n">
+        <v>15</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Nynäshamn</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Nynäshamn</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2020-07-15</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2020-07-15</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Kalvö 1:6, beställare: Nynäshamns kommun</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Lilian Karlsson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Lilian Karlsson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>87664490</v>
+      </c>
+      <c r="B57" t="n">
+        <v>99097</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>223609</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Vanlig skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine subsp. helleborine</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Kalvö 1:6, Srm</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>669353</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6536918</v>
+      </c>
+      <c r="S57" t="n">
+        <v>15</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Nynäshamn</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Nynäshamn</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2020-07-15</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2020-07-15</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Kalvö 1:6, beställare: Nynäshamns kommun</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Lilian Karlsson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Lilian Karlsson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>87664491</v>
+      </c>
+      <c r="B58" t="n">
+        <v>99097</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>223609</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Vanlig skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine subsp. helleborine</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Kalvö 1:6, Srm</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>669364</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6536917</v>
+      </c>
+      <c r="S58" t="n">
+        <v>15</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Nynäshamn</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Nynäshamn</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2020-07-15</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2020-07-15</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Kalvö 1:6, beställare: Nynäshamns kommun</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Lilian Karlsson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Lilian Karlsson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>87664493</v>
+      </c>
+      <c r="B59" t="n">
+        <v>99097</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>223609</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Vanlig skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine subsp. helleborine</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Kalvö 1:6, Srm</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>669266</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6536951</v>
+      </c>
+      <c r="S59" t="n">
+        <v>15</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Nynäshamn</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Nynäshamn</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2020-06-23</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2020-06-23</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Kalvö 1:6, beställare: Nynäshamns kommun</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Lilian Karlsson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Lilian Karlsson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>87664496</v>
+      </c>
+      <c r="B60" t="n">
+        <v>99097</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>223609</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Vanlig skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine subsp. helleborine</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Kalvö 1:6, Srm</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>669259</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6536955</v>
+      </c>
+      <c r="S60" t="n">
+        <v>15</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Nynäshamn</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Nynäshamn</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2020-06-23</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2020-06-23</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Kalvö 1:6, beställare: Nynäshamns kommun</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Lilian Karlsson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Lilian Karlsson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>87664521</v>
+      </c>
+      <c r="B61" t="n">
+        <v>99097</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>223609</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Vanlig skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine subsp. helleborine</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Kalvö 1:6, Srm</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>669287</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6536802</v>
+      </c>
+      <c r="S61" t="n">
+        <v>8</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Nynäshamn</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Nynäshamn</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2020-06-23</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2020-07-15</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Kalvö 1:6, beställare: Nynäshamns kommun</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Lilian Karlsson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Lilian Karlsson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>87664522</v>
+      </c>
+      <c r="B62" t="n">
+        <v>99097</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>223609</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Vanlig skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine subsp. helleborine</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Kalvö 1:6, Srm</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>669219</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6536840</v>
+      </c>
+      <c r="S62" t="n">
+        <v>8</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Nynäshamn</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Nynäshamn</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2020-06-23</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2020-07-15</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Kalvö 1:6, beställare: Nynäshamns kommun</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Lilian Karlsson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Lilian Karlsson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>87664523</v>
+      </c>
+      <c r="B63" t="n">
+        <v>99097</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>223609</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Vanlig skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine subsp. helleborine</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Kalvö 1:6, Srm</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>669223</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6536856</v>
+      </c>
+      <c r="S63" t="n">
+        <v>6</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Nynäshamn</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Nynäshamn</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2020-06-23</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2020-07-15</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Kalvö 1:6, beställare: Nynäshamns kommun</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Lilian Karlsson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Lilian Karlsson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>87664524</v>
+      </c>
+      <c r="B64" t="n">
+        <v>99097</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>223609</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Vanlig skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine subsp. helleborine</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Kalvö 1:6, Srm</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>669348</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6536771</v>
+      </c>
+      <c r="S64" t="n">
+        <v>8</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Nynäshamn</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Nynäshamn</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2020-06-23</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2020-07-15</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Kalvö 1:6, beställare: Nynäshamns kommun</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Lilian Karlsson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Lilian Karlsson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>87664526</v>
+      </c>
+      <c r="B65" t="n">
+        <v>99097</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>223609</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Vanlig skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine subsp. helleborine</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Kalvö 1:6, Srm</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>669283</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6536850</v>
+      </c>
+      <c r="S65" t="n">
+        <v>6</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Nynäshamn</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Nynäshamn</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2020-06-23</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2020-07-15</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Kalvö 1:6, beställare: Nynäshamns kommun</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Lilian Karlsson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Lilian Karlsson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>87664527</v>
+      </c>
+      <c r="B66" t="n">
+        <v>99097</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>223609</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Vanlig skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine subsp. helleborine</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Kalvö 1:6, Srm</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>669247</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6536953</v>
+      </c>
+      <c r="S66" t="n">
+        <v>8</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Nynäshamn</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Nynäshamn</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2020-06-23</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2020-07-15</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Kalvö 1:6, beställare: Nynäshamns kommun</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Lilian Karlsson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Lilian Karlsson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 18378-2026 artfynd.xlsx
+++ b/artfynd/A 18378-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY66"/>
+  <dimension ref="A1:AZ66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -785,6 +790,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87556027</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -887,6 +897,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87664529</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1015,6 +1030,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131580328</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1122,6 +1142,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87664488</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1234,6 +1259,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87664512</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1346,6 +1376,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86777385</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1458,6 +1493,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86778399</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1566,6 +1606,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86778658</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1683,6 +1728,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87554993</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1805,6 +1855,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87555100</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1922,6 +1977,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87555212</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2044,6 +2104,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87555228</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2161,6 +2226,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87555248</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2273,6 +2343,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87555369</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2390,6 +2465,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87555461</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2502,6 +2582,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87555491</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2619,6 +2704,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87555519</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2736,6 +2826,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87555538</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2858,6 +2953,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87555569</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2975,6 +3075,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87555609</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3097,6 +3202,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87555630</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3219,6 +3329,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87555754</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3331,6 +3446,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87555882</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3448,6 +3568,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87555911</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3570,6 +3695,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87555929</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3692,6 +3822,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87556049</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3800,6 +3935,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87556102</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3922,6 +4062,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87556145</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4044,6 +4189,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87556173</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4156,6 +4306,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87556190</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4278,6 +4433,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87556251</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4400,6 +4560,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87556392</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4522,6 +4687,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87556462</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4630,6 +4800,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87556485</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4752,6 +4927,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87556505</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4874,6 +5054,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87556734</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4996,6 +5181,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87556748</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5108,6 +5298,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87556777</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5230,6 +5425,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87556824</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5347,6 +5547,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87557077</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5469,6 +5674,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87557201</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5591,6 +5801,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87557237</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5703,6 +5918,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87557271</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5825,6 +6045,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87557291</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5947,6 +6172,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87557344</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6069,6 +6299,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87557940</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6177,6 +6412,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86778677</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6279,6 +6519,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87664485</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6381,6 +6626,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87664492</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6483,6 +6733,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87664500</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6595,6 +6850,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86778724</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6697,6 +6957,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87664502</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6799,6 +7064,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87664505</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6897,6 +7167,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87664486</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6995,6 +7270,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87664489</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7102,6 +7382,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87664490</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7200,6 +7485,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87664491</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7298,6 +7588,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87664493</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7405,6 +7700,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87664496</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7512,6 +7812,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87664521</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7619,6 +7924,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87664522</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7726,6 +8036,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87664523</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7824,6 +8139,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87664524</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7922,6 +8242,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87664526</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -8020,8 +8345,80 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87664527</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>